--- a/output/_temp/etapa_1_limpieza_base/cierre_ot_base_tecnico.xlsx
+++ b/output/_temp/etapa_1_limpieza_base/cierre_ot_base_tecnico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G232"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,20 +460,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03648736</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>03649003</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RF-4 SAN NICOLAS</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SIGADM</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46027</v>
+        <v>46128</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -481,24 +485,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03648748</t>
+          <t>03649004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ESTACION COPAQUIRE</t>
+          <t>RF-4 SAN NICOLAS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SIGAIR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46027</v>
+        <v>46128</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -506,24 +510,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03648749</t>
+          <t>03649057</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESTACION COPAQUIRE</t>
+          <t>MAH-01 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SIGAIR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46027</v>
+        <v>46128</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -531,24 +535,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03648750</t>
+          <t>03649058</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rosario</t>
+          <t>MAH-01 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SIGAIR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -556,24 +560,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03648754</t>
+          <t>03649190</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 4</t>
+          <t>QYA YABRICOYITA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -581,24 +585,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03648757</t>
+          <t>03649191</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 2A</t>
+          <t>QYA YABRICOYITA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -606,24 +610,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03648759</t>
+          <t>03649194</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sensor NE TK-33</t>
+          <t>PUNTERA 1 (P-01)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -631,24 +635,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03648764</t>
+          <t>03649195</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 3B</t>
+          <t>PUNTERA 1 (P-01)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -656,24 +660,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03648766</t>
+          <t>03649200</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 10</t>
+          <t>PUNTERA 2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -681,12 +685,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03648877</t>
+          <t>03649201</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ADTR LIXIVIACIÓN</t>
+          <t>PUNTERA 2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -695,10 +699,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -706,12 +710,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03648878</t>
+          <t>03649212</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MTP-17 TRANQUE</t>
+          <t>RF-1 YABRICOLLITA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -731,12 +735,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03648879</t>
+          <t>03649213</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MTP-17</t>
+          <t>RF-1 YABRICOLLITA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -745,10 +749,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -756,12 +760,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03648880</t>
+          <t>03649214</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FAD PUERTO COLLAHUASI</t>
+          <t>RF-2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -770,10 +774,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -781,12 +785,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03648881</t>
+          <t>03649215</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LPDC-01 LIXIVIACIÓN</t>
+          <t>RF-2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -795,10 +799,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -806,12 +810,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03648882</t>
+          <t>03649222</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LPDC-01 LIXIVIACIÓN</t>
+          <t>RF-05 Chiclla</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -820,10 +824,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -831,12 +835,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>03648883</t>
+          <t>03649223</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LPDC-02 LIXIVIACIÓN</t>
+          <t>RF-05 Chiclla</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -845,10 +849,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -856,12 +860,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03648884</t>
+          <t>03649224</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LPDC-02 LIXIVIACIÓN</t>
+          <t>CGP PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -870,10 +874,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -881,12 +885,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03648885</t>
+          <t>03677147</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPDC-03 LIXIVIACIÓN</t>
+          <t>CPPCHE PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -895,10 +899,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -906,12 +910,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03648886</t>
+          <t>03677148</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LPDC-03 LIXIVIACIÓN</t>
+          <t>CGP PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -920,10 +924,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -931,12 +935,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03648887</t>
+          <t>03677149</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LPDC-04 LIXIVIACIÓN</t>
+          <t>CPPCHE PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -945,10 +949,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -956,24 +960,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>03648888</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LPDC-04 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03675515</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -981,24 +981,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>03648889</t>
+          <t>03678603</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LPDC-05 LIXIVIACIÓN</t>
+          <t>Estacion Calidad del aire Puerto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46207</v>
+        <v>46132</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1006,12 +1006,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>03648890</t>
+          <t>03661667</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LPDC-05 LIXIVIACIÓN</t>
+          <t>R-B-2 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1031,12 +1031,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>03648891</t>
+          <t>03661668</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LPDC-06 LIXIVIACIÓN</t>
+          <t>R-C-1 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1056,12 +1056,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>03648892</t>
+          <t>03661669</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LPDC-06 LIXIVIACIÓN</t>
+          <t>R-C-2 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1081,12 +1081,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>03648893</t>
+          <t>03661670</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LPDC-07 LIXIVIACIÓN</t>
+          <t>R-C-3B  COPOSA NORTE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1106,12 +1106,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>03648894</t>
+          <t>03661671</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LPDC-07 LIXIVIACIÓN</t>
+          <t>R-PORT-1 PORTEZUELO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1131,12 +1131,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>03648895</t>
+          <t>03661672</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LPDC-08 LIXIVIACIÓN</t>
+          <t>PEP-04C PORTEZUELO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1156,12 +1156,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>03648896</t>
+          <t>03661673</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LPDC-08 LIXIVIACIÓN</t>
+          <t>PEP-04C PORTEZUELO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1181,12 +1181,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>03649005</t>
+          <t>03661674</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P-4B MICHINCHA</t>
+          <t>PEP-03 PORTEZUELO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -1206,12 +1206,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>03649006</t>
+          <t>03661675</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P-4B MICHINCHA</t>
+          <t>PEP-03 PORTEZUELO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -1231,12 +1231,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>03649007</t>
+          <t>03661743</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RPW-3 LIXIVIACIÓN</t>
+          <t>CWE-25 (2) COPOSA NORTE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -1256,12 +1256,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>03649008</t>
+          <t>03661744</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RPW-3 LIXIVIACIÓN</t>
+          <t>CWE-25 (3) COPOSA NORTE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
@@ -1281,12 +1281,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>03649009</t>
+          <t>03661754</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RPW-4 LIXIVIACIÓN</t>
+          <t>CWE-07 COPOSA SUR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -1306,12 +1306,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>03649010</t>
+          <t>03661779</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RPW-4 LIXIVIACIÓN</t>
+          <t>PEC-02 PORTEZUELO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1331,12 +1331,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>03649011</t>
+          <t>03661780</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RPW-1 LIXIVIACIÓN</t>
+          <t>PEP-02  PORTEZUELO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -1356,12 +1356,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>03649012</t>
+          <t>03661783</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RPW-1 LIXIVIACIÓN</t>
+          <t>PPC-01A COPOSA NORTE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1381,12 +1381,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>03649013</t>
+          <t>03661784</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>P-6 MICHINCHA</t>
+          <t>PPC-02 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1406,12 +1406,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>03649014</t>
+          <t>03661785</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>P-6 MICHINCHA</t>
+          <t>PPC-07 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -1431,12 +1431,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>03649015</t>
+          <t>03661786</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RPW-2  TRANQUE</t>
+          <t>PPC-09 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -1456,12 +1456,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>03649016</t>
+          <t>03661787</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RPW-2  TRANQUE</t>
+          <t>PPC-10 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -1481,12 +1481,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>03649017</t>
+          <t>03661788</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CSW-02 JACHUCOPOSA</t>
+          <t>PPC-14 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
@@ -1506,12 +1506,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>03649024</t>
+          <t>03661789</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CPMA-01 JACHUCOPOSA</t>
+          <t>PPC-15 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
@@ -1531,12 +1531,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>03649040</t>
+          <t>03661790</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>M-13 MICHINCHA</t>
+          <t>PPC-20 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -1556,12 +1556,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>03649041</t>
+          <t>03661791</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M-13 MICHINCHA</t>
+          <t>PPC-21 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1581,12 +1581,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>03649042</t>
+          <t>03661792</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>M-16 MICHINCHA</t>
+          <t>PPC-29 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -1606,12 +1606,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>03649043</t>
+          <t>03661826</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>M-16 MICHINCHA</t>
+          <t>PEP-01 PORTEZUELO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
@@ -1631,12 +1631,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>03649044</t>
+          <t>03661827</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>M-17 MICHINCHA</t>
+          <t>PEP-01 PORTEZUELO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
@@ -1656,12 +1656,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>03649045</t>
+          <t>03661830</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>M-17 MICHINCHA</t>
+          <t>RF-3 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
@@ -1681,12 +1681,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>03649046</t>
+          <t>03661831</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>M-18 MICHINCHA</t>
+          <t>RF-3 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
@@ -1706,24 +1706,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>03649047</t>
+          <t>03661846</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>M-18 MICHINCHA</t>
+          <t>DE AGUA. Lisimetro/Evaporimetro</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
@@ -1731,24 +1731,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>03649048</t>
+          <t>03661848</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>M-19 MICHINCHA</t>
+          <t>DE AGUA. Lisimetro/Evaporimetro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -1756,24 +1756,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>03649062</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MAU-13 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03670809</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46207</v>
+        <v>46132</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
@@ -1781,24 +1777,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>03649063</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MAU-02 MICHINCHA</t>
-        </is>
-      </c>
+          <t>03670810</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46207</v>
+        <v>46132</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
@@ -1806,12 +1798,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>03649064</t>
+          <t>03668548</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MAU-02 MICHINCHA</t>
+          <t>MITIGACION JACHUCOPOSA (CP-03M)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1820,10 +1812,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
@@ -1831,12 +1823,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>03649067</t>
+          <t>03668549</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MAU-13 LIXIVIACIÓN</t>
+          <t>CP-01-I FALLA PABELLON</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1845,10 +1837,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
@@ -1856,12 +1848,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>03649069</t>
+          <t>03668550</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MIT-01B LIXIVIACIÓN</t>
+          <t>CP-02-C FALLA PABELLON</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1870,10 +1862,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
@@ -1881,12 +1873,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>03649070</t>
+          <t>03668551</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MIT-02B LIXIVIACIÓN</t>
+          <t>CP-03-M FALLA PABELLON</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1895,10 +1887,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
@@ -1906,12 +1898,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>03649071</t>
+          <t>03668552</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MIT-03 LIXIVIACIÓN</t>
+          <t>CP-04-L FALLA PABELLON</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1920,10 +1912,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
@@ -1931,12 +1923,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>03649072</t>
+          <t>03668553</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MIT-01B LIXIVIACIÓN</t>
+          <t>CP-05-H FALLA PABELLON</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1945,10 +1937,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
@@ -1956,12 +1948,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03649073</t>
+          <t>03668554</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MIT-02B LIXIVIACIÓN</t>
+          <t>CP-06-J FALLA PABELLON</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1970,10 +1962,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
@@ -1981,12 +1973,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>03649074</t>
+          <t>03668555</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MIT-03 LIXIVIACIÓN</t>
+          <t>CP-07-F FALLA PABELLON</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1995,10 +1987,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
@@ -2006,12 +1998,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>03649075</t>
+          <t>03668556</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MMA-01 MICHINCHA</t>
+          <t>CP-08-D FALLA PABELLON</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2020,10 +2012,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -2031,12 +2023,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>03649076</t>
+          <t>03668557</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MMA-02 MICHINCHA</t>
+          <t>CP-09-G FALLA PABELLON</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2045,10 +2037,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
@@ -2056,12 +2048,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>03649077</t>
+          <t>03668558</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MMA-03 MICHINCHA</t>
+          <t>CP-10-B FALLA PABELLON</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2070,10 +2062,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
@@ -2081,12 +2073,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>03649078</t>
+          <t>03668559</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MMA-04 MICHINCHA</t>
+          <t>CP-11-E FALLA PABELLON</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2095,10 +2087,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
@@ -2106,12 +2098,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>03649079</t>
+          <t>03668560</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MMA-05 MICHINCHA</t>
+          <t>CP-12-K FALLA PABELLON</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2120,10 +2112,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
@@ -2131,12 +2123,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>03649080</t>
+          <t>03668561</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MMA-06 MICHINCHA</t>
+          <t>CP-13-A FALLA PABELLON</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2145,10 +2137,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
@@ -2156,12 +2148,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>03649081</t>
+          <t>03668562</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MMA-07 MICHINCHA</t>
+          <t>CPS-20 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2170,10 +2162,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
@@ -2181,12 +2173,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>03649082</t>
+          <t>03668563</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MMA-08 MICHINCHA</t>
+          <t>CPS-23 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
@@ -2206,12 +2198,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>03649083</t>
+          <t>03668564</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MMA-09 MICHINCHA</t>
+          <t>CPS-54 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2220,10 +2212,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
@@ -2231,12 +2223,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>03649084</t>
+          <t>03668565</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MMA-10 MICHINCHA</t>
+          <t>CPS-55 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2245,10 +2237,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
@@ -2256,12 +2248,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03649085</t>
+          <t>03668566</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MMA-11 MICHINCHA</t>
+          <t>CPZ-08C JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2270,10 +2262,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
@@ -2281,12 +2273,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>03649086</t>
+          <t>03668574</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MMA-12 MICHINCHA</t>
+          <t>CPZ-07A JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2295,10 +2287,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
@@ -2306,12 +2298,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>03649087</t>
+          <t>03668575</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MMA-13 MICHINCHA</t>
+          <t>CWE-12 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2320,10 +2312,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
@@ -2331,12 +2323,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>03649088</t>
+          <t>03668579</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MMA-14 MICHINCHA</t>
+          <t>CWE-01 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2345,10 +2337,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
@@ -2356,12 +2348,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>03649089</t>
+          <t>03668581</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MMA-01 MICHINCHA</t>
+          <t>CWE-06 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2370,10 +2362,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
@@ -2381,12 +2373,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>03649090</t>
+          <t>03668584</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MMA-02 MICHINCHA</t>
+          <t>CWE-12 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2395,10 +2387,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
@@ -2406,12 +2398,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>03649091</t>
+          <t>03668585</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MMA-03 MICHINCHA</t>
+          <t>CWE-19 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2420,10 +2412,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
@@ -2431,12 +2423,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>03649092</t>
+          <t>03668591</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MMA-04 MICHINCHA</t>
+          <t>CWE-01 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2445,10 +2437,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
@@ -2456,12 +2448,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>03649093</t>
+          <t>03668592</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MMA-05 MICHINCHA</t>
+          <t>CWE-06 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2470,10 +2462,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
@@ -2481,12 +2473,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>03649094</t>
+          <t>03668594</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MMA-06 MICHINCHA</t>
+          <t>CWP-14 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2495,10 +2487,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
@@ -2506,12 +2498,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>03649095</t>
+          <t>03668595</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MMA-07 MICHINCHA</t>
+          <t>CWP-14 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2520,10 +2512,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
@@ -2531,24 +2523,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>03649096</t>
+          <t>03668596</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MMA-08 MICHINCHA</t>
+          <t>DEC-06B COPOSA SUR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGVANC</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
@@ -2556,12 +2548,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>03649097</t>
+          <t>03668599</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MMA-09 MICHINCHA</t>
+          <t>JCC-4 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2570,10 +2562,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
@@ -2581,12 +2573,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>03649098</t>
+          <t>03668600</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MMA-10 MICHINCHA</t>
+          <t>JCC-5 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2595,10 +2587,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E87" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
@@ -2606,12 +2598,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>03649099</t>
+          <t>03668601</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MMA-11 MICHINCHA</t>
+          <t>M-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2620,10 +2612,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
@@ -2631,12 +2623,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>03649100</t>
+          <t>03668602</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MMA-12 MICHINCHA</t>
+          <t>M-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2645,10 +2637,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
@@ -2656,24 +2648,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>03649101</t>
+          <t>03668603</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MMA-13 MICHINCHA</t>
+          <t>MA-08 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGVANC</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
@@ -2681,12 +2673,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>03649102</t>
+          <t>03668604</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MMA-14 MICHINCHA</t>
+          <t>MAU-01B LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2695,10 +2687,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
@@ -2706,12 +2698,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>03649103</t>
+          <t>03668605</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MPZ-10A LIXIVIACIÓN</t>
+          <t>MAU-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2720,10 +2712,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
@@ -2731,12 +2723,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>03649104</t>
+          <t>03668606</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MPZ-10B LIXIVIACIÓN</t>
+          <t>MAU-01B LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2745,10 +2737,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
@@ -2756,12 +2748,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>03649105</t>
+          <t>03668607</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MPZ-11B MICHINCHA</t>
+          <t>MAU-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2770,10 +2762,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
@@ -2781,12 +2773,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>03649106</t>
+          <t>03668608</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MPZ-11B MICHINCHA</t>
+          <t>MTP-11 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2795,10 +2787,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
@@ -2806,12 +2798,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>03649109</t>
+          <t>03668609</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MPZ-10A LIXIVIACIÓN</t>
+          <t>MTP-11 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2820,10 +2812,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
@@ -2831,12 +2823,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>03649110</t>
+          <t>03668610</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MPZ-10B LIXIVIACIÓN</t>
+          <t>MTP-15 TRANQUE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2845,10 +2837,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
@@ -2856,12 +2848,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>03649111</t>
+          <t>03668611</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MSW-1A MICHINCHA</t>
+          <t>MTP-16 TRANQUE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2870,10 +2862,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
@@ -2881,12 +2873,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>03649112</t>
+          <t>03668612</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MSW-2 MICHINCHA</t>
+          <t>MTP-20 TRANQUE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2895,10 +2887,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
@@ -2906,12 +2898,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>03649113</t>
+          <t>03668613</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MSW-2 MICHINCHA</t>
+          <t>MTP-16 TRANQUE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2920,10 +2912,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E100" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
@@ -2931,12 +2923,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>03649114</t>
+          <t>03668620</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MTP-13 MICHINCHA</t>
+          <t>PMA-03 UJINA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2945,10 +2937,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
@@ -2956,12 +2948,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>03649115</t>
+          <t>03668625</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MTP-13 MICHINCHA</t>
+          <t>PQY-02 YABRICOYITA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2970,10 +2962,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E102" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
@@ -2981,12 +2973,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>03649116</t>
+          <t>03668626</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MTP-09 TRANQUE</t>
+          <t>PQY-03 YABRICOYITA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2995,10 +2987,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
@@ -3006,12 +2998,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>03649117</t>
+          <t>03668627</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MTP-09 TRANQUE</t>
+          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3020,10 +3012,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
@@ -3031,12 +3023,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>03649118</t>
+          <t>03668628</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MTP-14 TRANQUE</t>
+          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3045,10 +3037,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E105" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
@@ -3056,12 +3048,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>03649119</t>
+          <t>03668633</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MTP-14 TRANQUE</t>
+          <t>SH-19 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3070,10 +3062,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
@@ -3081,12 +3073,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>03649127</t>
+          <t>03668634</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PLIX-01A LIXIVIACIÓN</t>
+          <t>SH-20 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3095,10 +3087,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E107" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
@@ -3106,12 +3098,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>03649128</t>
+          <t>03668635</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PLIX-01B LIXIVIACIÓN</t>
+          <t>SH-22 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3120,10 +3112,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
@@ -3131,12 +3123,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>03649129</t>
+          <t>03668636</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PLIX-02A LIXIVIACIÓN</t>
+          <t>SH-23 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3145,10 +3137,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E109" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
@@ -3156,12 +3148,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>03649130</t>
+          <t>03668637</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PLIX-02B LIXIVIACIÓN</t>
+          <t>SH-20 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3170,10 +3162,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
@@ -3181,12 +3173,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>03649131</t>
+          <t>03668638</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PLIX-03A LIXIVIACIÓN</t>
+          <t>SH-22 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3195,10 +3187,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E111" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
@@ -3206,12 +3198,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>03649132</t>
+          <t>03668639</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PLIX-03B LIXIVIACIÓN</t>
+          <t>SH-23 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3220,10 +3212,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E112" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
@@ -3231,12 +3223,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>03649133</t>
+          <t>03668640</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PLIX-04 LIXIVIACIÓN</t>
+          <t>Piscina P2 ROSARIO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3245,10 +3237,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E113" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
@@ -3256,12 +3248,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>03649134</t>
+          <t>03668641</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PLIX-05A LIXIVIACIÓN</t>
+          <t>ARR- 1 (Piscina P2)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3270,10 +3262,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E114" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
@@ -3281,12 +3273,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>03649135</t>
+          <t>03668645</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PLIX-05B LIXIVIACIÓN</t>
+          <t>Piscina P3 ROSARIO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3295,10 +3287,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E115" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
@@ -3306,24 +3298,24 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>03649136</t>
+          <t>03670812</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PLIX-06 LIXIVIACIÓN</t>
+          <t>Casino 460</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E116" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
@@ -3331,24 +3323,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>03649137</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>PLIX-07A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671634</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E117" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
@@ -3356,24 +3344,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>03649138</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>PLIX-07B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671635</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E118" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
@@ -3381,24 +3365,24 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>03649139</t>
+          <t>03671636</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PLIX-08A LIXIVIACIÓN</t>
+          <t>REPORTE PAT FRONTERA (Dashboard nivel y cauda</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E119" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
@@ -3406,24 +3390,20 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>03649140</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>PLIX-08B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671637</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E120" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
@@ -3431,24 +3411,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>03649141</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>PLIX-09 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671638</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E121" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
@@ -3456,24 +3432,20 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>03649142</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>PLIX-10A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671639</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E122" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
@@ -3481,24 +3453,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>03649143</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>PLIX-10B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686123</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E123" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
@@ -3506,24 +3474,20 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>03649144</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>PLIX-11A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686126</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
@@ -3531,24 +3495,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>03649145</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>PLIX-11B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686127</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E125" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
@@ -3556,24 +3516,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>03649146</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>PLIX-12B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686128</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
@@ -3581,24 +3537,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>03649147</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>PLIX-13A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686137</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E127" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
@@ -3606,12 +3558,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>03649148</t>
+          <t>03676987</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PLIX-13B LIXIVIACIÓN</t>
+          <t>OFICINAS  SI ENERGIA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3620,10 +3572,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E128" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
@@ -3631,12 +3583,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>03649149</t>
+          <t>03676988</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PLIX-14 LIXIVIACIÓN</t>
+          <t>BCON UJINA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3645,10 +3597,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E129" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
@@ -3656,12 +3608,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>03649150</t>
+          <t>03676989</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PLIX-01A LIXIVIACIÓN</t>
+          <t>BGSO UJINA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3670,10 +3622,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E130" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
@@ -3681,12 +3633,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>03649151</t>
+          <t>03676990</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PLIX-01B LIXIVIACIÓN</t>
+          <t>ZANJA NORTE 2 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3695,10 +3647,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E131" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
@@ -3706,12 +3658,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>03649152</t>
+          <t>03676991</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PLIX-02A LIXIVIACIÓN</t>
+          <t>PTAS PUERTO COLLAHUASI PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3720,10 +3672,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E132" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
@@ -3731,12 +3683,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>03649153</t>
+          <t>03676992</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PLIX-02B LIXIVIACIÓN</t>
+          <t>ZANJA NORTE 1 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3745,10 +3697,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E133" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
@@ -3756,12 +3708,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>03649154</t>
+          <t>03676993</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PLIX-03A LIXIVIACIÓN</t>
+          <t>PTAS-C FALLA PABELLON</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3770,10 +3722,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E134" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
@@ -3781,12 +3733,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>03649155</t>
+          <t>03676994</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PLIX-03B LIXIVIACIÓN</t>
+          <t>TK-505 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3795,10 +3747,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E135" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
@@ -3806,12 +3758,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>03649156</t>
+          <t>03676995</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PLIX-04 LIXIVIACIÓN</t>
+          <t>CSW-02 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3820,10 +3772,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E136" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
@@ -3831,12 +3783,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>03649157</t>
+          <t>03676996</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PLIX-05A LIXIVIACIÓN</t>
+          <t>BPCR ROSARIO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3845,10 +3797,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E137" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
@@ -3856,12 +3808,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>03649158</t>
+          <t>03676997</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PLIX-05B LIXIVIACIÓN</t>
+          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3870,10 +3822,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E138" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
@@ -3881,12 +3833,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>03649159</t>
+          <t>03676998</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PLIX-06 LIXIVIACIÓN</t>
+          <t>QDH-2 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3895,10 +3847,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E139" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
@@ -3906,12 +3858,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>03649160</t>
+          <t>03676999</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PLIX-07A LIXIVIACIÓN</t>
+          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3920,10 +3872,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E140" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
@@ -3931,12 +3883,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>03649161</t>
+          <t>03677000</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PLIX-07B LIXIVIACIÓN</t>
+          <t>QSN-1 SAN NICOLAS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3945,10 +3897,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E141" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
@@ -3956,12 +3908,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>03649162</t>
+          <t>03677001</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PLIX-08A LIXIVIACIÓN</t>
+          <t>SH-02B PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3970,10 +3922,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E142" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
@@ -3981,12 +3933,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>03649163</t>
+          <t>03677002</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PLIX-08B LIXIVIACIÓN</t>
+          <t>SH-06 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3995,10 +3947,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E143" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
@@ -4006,12 +3958,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>03649164</t>
+          <t>03677003</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PLIX-09 LIXIVIACIÓN</t>
+          <t>SH-07 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4020,10 +3972,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E144" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
@@ -4031,12 +3983,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>03649165</t>
+          <t>03677004</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PLIX-10A LIXIVIACIÓN</t>
+          <t>SH-08 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4045,10 +3997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E145" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
@@ -4056,12 +4008,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>03649166</t>
+          <t>03677005</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PLIX-10B LIXIVIACIÓN</t>
+          <t>SH-19 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4070,10 +4022,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E146" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
@@ -4081,12 +4033,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>03649167</t>
+          <t>03677006</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PLIX-11A LIXIVIACIÓN</t>
+          <t>CPC FALLA PABELLON</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4095,10 +4047,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E147" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
@@ -4106,12 +4058,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>03649168</t>
+          <t>03677007</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PLIX-11B LIXIVIACIÓN</t>
+          <t>C-1000 UJINA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4120,10 +4072,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E148" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
@@ -4131,12 +4083,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>03649169</t>
+          <t>03677008</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PLIX-12B LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS BCC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4145,10 +4097,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E149" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
@@ -4156,12 +4108,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>03649170</t>
+          <t>03677009</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PLIX-13A LIXIVIACIÓN</t>
+          <t>C-460 ROSARIO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4170,10 +4122,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E150" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
@@ -4181,12 +4133,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>03649171</t>
+          <t>03677010</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PLIX-13B LIXIVIACIÓN</t>
+          <t>CCD</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4195,10 +4147,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E151" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
@@ -4206,12 +4158,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>03649172</t>
+          <t>03677011</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PLIX-14 LIXIVIACIÓN</t>
+          <t>TK-1004 ROSARIO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4220,10 +4172,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E152" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
@@ -4231,12 +4183,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>03649179</t>
+          <t>03677012</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PMI-01 MICHINCHA</t>
+          <t>TK-517 UJINA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4245,10 +4197,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E153" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
@@ -4256,12 +4208,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>03649180</t>
+          <t>03677013</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PMI-01 MICHINCHA</t>
+          <t>PTAS-M ROSARIO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4270,10 +4222,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E154" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
@@ -4281,12 +4233,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>03649185</t>
+          <t>03677014</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PR  PUERTO COLLAHUASI</t>
+          <t>BOR ROSARIO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4295,10 +4247,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
@@ -4306,12 +4258,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>03649186</t>
+          <t>03677015</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
+          <t>PISCINA  DIQUE HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4320,10 +4272,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
@@ -4331,24 +4283,24 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>03649188</t>
+          <t>03679194</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
+          <t>Ujina</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E157" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
@@ -4356,24 +4308,24 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>03649206</t>
+          <t>03679195</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Estación 1</t>
+          <t>Ujina</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E158" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
@@ -4381,24 +4333,24 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>03649207</t>
+          <t>03679196</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Piscina P3 ROSARIO</t>
+          <t>Coposa Continuo</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E159" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
@@ -4406,24 +4358,24 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>03649216</t>
+          <t>03679197</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LPDC-09 LIXIVIACIÓN</t>
+          <t>Coposa EMRP Discreto</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E160" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
@@ -4431,24 +4383,24 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>03649217</t>
+          <t>03679236</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LPDC-09 LIXIVIACIÓN</t>
+          <t>Casino 460</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E161" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
@@ -4456,24 +4408,24 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>03649218</t>
+          <t>03679237</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LPDC-10 LIXIVIACIÓN</t>
+          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGADM</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E162" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
@@ -4481,24 +4433,24 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>03649219</t>
+          <t>03679238</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LPDC-10 LIXIVIACIÓN</t>
+          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGADM</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E163" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
@@ -4506,24 +4458,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>03649220</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>LPDC-11 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03679277</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E164" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
@@ -4531,24 +4479,20 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>03649221</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>LPDC-11 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03679278</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E165" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
@@ -4556,24 +4500,20 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>03649238</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>PAR PUERTO COLLAHUASI</t>
-        </is>
-      </c>
+          <t>03679279</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E166" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
@@ -4581,24 +4521,24 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>03649239</t>
+          <t>03687291</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PEV-01 (PES-01) PUERTO COLLAHUASI</t>
+          <t>BODEGA SIGA-B02</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E167" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
@@ -4606,24 +4546,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>03649240</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>CWE-18 (1) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03687292</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGADM</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E168" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
@@ -4631,24 +4567,24 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>03649241</t>
+          <t>03687293</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CWE-18 (2) FALLA PABELLON</t>
+          <t>PISCINA DIQUE SAN DANIEL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E169" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
@@ -4656,24 +4592,20 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>03649242</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>CWE-23 (1) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03679280</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46207</v>
+        <v>46130</v>
       </c>
       <c r="E170" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
@@ -4681,24 +4613,20 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>03649243</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>CWE-23 (2) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03679281</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E171" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
@@ -4706,24 +4634,20 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>03649244</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>CWE-23 (3) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03679282</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E172" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
@@ -4731,24 +4655,20 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>03649245</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>CWE-23 (4) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03679283</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E173" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
@@ -4756,24 +4676,20 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>03649246</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>M-09 MICHINCHA</t>
-        </is>
-      </c>
+          <t>03679284</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E174" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
@@ -4781,24 +4697,20 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>03649247</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>M-28 MICHINCHA</t>
-        </is>
-      </c>
+          <t>03679285</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E175" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
@@ -4806,24 +4718,24 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>03649248</t>
+          <t>03679286</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>UC-602 LIXIVIACIÓN</t>
+          <t>REPORTE POZOS  MICHINCHA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E176" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
@@ -4831,24 +4743,20 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>03649249</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>UC-603 MICHINCHA</t>
-        </is>
-      </c>
+          <t>03679287</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E177" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
@@ -4856,20 +4764,24 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>03653640</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr"/>
+          <t>03679288</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>MM1: Dashboard niveles</t>
+        </is>
+      </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SIGEXT</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E178" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
@@ -4877,20 +4789,24 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>03653641</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr"/>
+          <t>03679289</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>REPORTE POZOS PUERTO</t>
+        </is>
+      </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SIGEXT</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E179" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
@@ -4898,20 +4814,20 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>03653642</t>
+          <t>03679290</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SIGEXT</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E180" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
@@ -4919,20 +4835,20 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>03660793</t>
+          <t>03679291</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E181" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
@@ -4940,24 +4856,24 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>03648737</t>
+          <t>03679292</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
+          <t>REPORTE PISCINAS P3-P2</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SIGADM</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46238</v>
+        <v>46133</v>
       </c>
       <c r="E182" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
@@ -4965,24 +4881,20 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>03648738</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
-        </is>
-      </c>
+          <t>03679293</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SIGADM</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46238</v>
+        <v>46133</v>
       </c>
       <c r="E183" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
@@ -4990,24 +4902,20 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>03661637</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>OFICINAS  SI ENERGIA</t>
-        </is>
-      </c>
+          <t>03679294</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46238</v>
+        <v>46134</v>
       </c>
       <c r="E184" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr"/>
@@ -5015,24 +4923,24 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>03661638</t>
+          <t>03679295</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>BCON UJINA</t>
+          <t>REPORTE PAT JACHUCOPOSA-COPOSITO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46238</v>
+        <v>46134</v>
       </c>
       <c r="E185" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
@@ -5040,24 +4948,24 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>03661639</t>
+          <t>03679296</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BGSO UJINA</t>
+          <t>REPORTE PAT TRANQUE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46238</v>
+        <v>46134</v>
       </c>
       <c r="E186" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
@@ -5065,1148 +4973,27 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>03661640</t>
+          <t>ES532MACWE          0001</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ZANJA NORTE 2 PUERTO COLLAHUASI</t>
+          <t>REPORTE BALANCE IONICO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46238</v>
+        <v>46134</v>
       </c>
       <c r="E187" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>03661641</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>PTAS PUERTO COLLAHUASI PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D188" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E188" t="n">
-        <v>4</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>03661642</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>ZANJA NORTE 1 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D189" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E189" t="n">
-        <v>4</v>
-      </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>03661643</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>PTAS-C FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D190" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E190" t="n">
-        <v>4</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>03661644</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>TK-505 FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D191" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E191" t="n">
-        <v>4</v>
-      </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>03661645</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>CSW-02 JACHUCOPOSA</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D192" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E192" t="n">
-        <v>4</v>
-      </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>03661646</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>BPCR ROSARIO</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D193" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E193" t="n">
-        <v>4</v>
-      </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>03661647</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D194" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E194" t="n">
-        <v>4</v>
-      </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>03661648</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>QDH-2 HUINQUINTIPA</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D195" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E195" t="n">
-        <v>4</v>
-      </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>03661649</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D196" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E196" t="n">
-        <v>4</v>
-      </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>03661650</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>QSN-1 SAN NICOLAS</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D197" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E197" t="n">
-        <v>4</v>
-      </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>03661651</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>SH-02B PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D198" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E198" t="n">
-        <v>4</v>
-      </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>03661652</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>SH-06 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D199" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E199" t="n">
-        <v>4</v>
-      </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>03661653</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>SH-07 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D200" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E200" t="n">
-        <v>4</v>
-      </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>03661654</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>SH-08 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D201" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E201" t="n">
-        <v>4</v>
-      </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>03661655</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>SH-19 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D202" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E202" t="n">
-        <v>4</v>
-      </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>03661656</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>CPC FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D203" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E203" t="n">
-        <v>4</v>
-      </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>03661657</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>C-1000 UJINA</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D204" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E204" t="n">
-        <v>4</v>
-      </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>03661658</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BCC</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D205" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E205" t="n">
-        <v>4</v>
-      </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>03661659</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>C-460 ROSARIO</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D206" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E206" t="n">
-        <v>4</v>
-      </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>03661660</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>CCD</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D207" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E207" t="n">
-        <v>4</v>
-      </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>03661661</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>TK-1004 ROSARIO</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D208" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E208" t="n">
-        <v>4</v>
-      </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>03661662</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>TK-517 UJINA</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D209" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E209" t="n">
-        <v>4</v>
-      </c>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>03661663</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>PTAS-M ROSARIO</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D210" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E210" t="n">
-        <v>4</v>
-      </c>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>03661664</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>BOR ROSARIO</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D211" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E211" t="n">
-        <v>4</v>
-      </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>03661665</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>PISCINA  DIQUE HUINQUINTIPA</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D212" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E212" t="n">
-        <v>4</v>
-      </c>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>03661838</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Ujina</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D213" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E213" t="n">
-        <v>4</v>
-      </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>03661839</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Ujina</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D214" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E214" t="n">
-        <v>4</v>
-      </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>03661840</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Coposa Continuo</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D215" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E215" t="n">
-        <v>4</v>
-      </c>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>03661841</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Coposa EMRP Discreto</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D216" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E216" t="n">
-        <v>4</v>
-      </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>03661842</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Casino 460</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D217" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E217" t="n">
-        <v>4</v>
-      </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>03670028</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>BODEGA SIGA-B02</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D218" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E218" t="n">
-        <v>4</v>
-      </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>03670029</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>SIGADM</t>
-        </is>
-      </c>
-      <c r="D219" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E219" t="n">
-        <v>4</v>
-      </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>03670030</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>PISCINA DIQUE SAN DANIEL</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D220" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E220" t="n">
-        <v>4</v>
-      </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>03649225</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>BCON UJINA</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D221" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E221" t="n">
-        <v>4</v>
-      </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>03649226</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>BGSO UJINA</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D222" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E222" t="n">
-        <v>4</v>
-      </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>03649227</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>TK-505 FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D223" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E223" t="n">
-        <v>4</v>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>03649228</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>BPCR ROSARIO</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D224" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E224" t="n">
-        <v>4</v>
-      </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>03649229</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>CPC FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D225" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E225" t="n">
-        <v>4</v>
-      </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>03649230</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>C-1000 UJINA</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D226" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E226" t="n">
-        <v>4</v>
-      </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>03649231</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BCC</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D227" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E227" t="n">
-        <v>4</v>
-      </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>03649232</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>C-460 ROSARIO</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D228" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E228" t="n">
-        <v>4</v>
-      </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>03649233</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>CCD</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D229" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E229" t="n">
-        <v>4</v>
-      </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>03649234</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>TK-1004 ROSARIO</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D230" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E230" t="n">
-        <v>4</v>
-      </c>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>03649235</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>TK-517 UJINA</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D231" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E231" t="n">
-        <v>4</v>
-      </c>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>03649236</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>BOR ROSARIO</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D232" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E232" t="n">
-        <v>4</v>
-      </c>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
